--- a/data/trans_orig/LAWTONB_2R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/LAWTONB_2R-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el nivel de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2007</t>
+          <t>Población según el grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>249282</t>
+          <t>249841</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>283086</t>
+          <t>281807</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>354435</t>
+          <t>356315</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>401365</t>
+          <t>403045</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>60,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>614005</t>
+          <t>615602</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>673458</t>
+          <t>671519</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>69,88%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>42152</t>
+          <t>43236</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>69172</t>
+          <t>68151</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>77553</t>
+          <t>77014</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>112222</t>
+          <t>112218</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,47 +896,47 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
+          <t>13,1%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>19,09%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>147807</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>126734</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>170352</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>15,38%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
           <t>13,19%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>19,09%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>147807</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>127807</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>171581</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>15,38%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>13,3%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,73%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11540</t>
+          <t>11801</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27799</t>
+          <t>27693</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>45202</t>
+          <t>44689</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>74495</t>
+          <t>76120</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>60846</t>
+          <t>62452</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>94310</t>
+          <t>96329</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>10,02%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11223</t>
+          <t>11521</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26914</t>
+          <t>26826</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15017</t>
+          <t>15340</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>35042</t>
+          <t>34517</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30367</t>
+          <t>30912</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>55367</t>
+          <t>54142</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9077</t>
+          <t>9265</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23782</t>
+          <t>23624</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>21720</t>
+          <t>22554</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>44637</t>
+          <t>46882</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>36666</t>
+          <t>35848</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>62791</t>
+          <t>64179</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,68%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>65199</t>
+          <t>65275</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>79190</t>
+          <t>79439</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,02%</t>
+          <t>74,11%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,9%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39623</t>
+          <t>41077</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54601</t>
+          <t>54639</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,69%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>110730</t>
+          <t>111905</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>131707</t>
+          <t>131473</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,67%</t>
+          <t>74,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,48%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1714</t>
+          <t>1747</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9819</t>
+          <t>9989</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1895</t>
+          <t>1933</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12610</t>
+          <t>12564</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>20,19%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5017</t>
+          <t>5431</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17804</t>
+          <t>18820</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2556</t>
+          <t>2523</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12057</t>
+          <t>13324</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8334</t>
+          <t>8173</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,14%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3677</t>
+          <t>3599</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15986</t>
+          <t>16007</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,65%</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5915</t>
+          <t>5893</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6769</t>
+          <t>6856</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10232</t>
+          <t>10302</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,85%</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5746</t>
+          <t>5577</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>909</t>
+          <t>925</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8614</t>
+          <t>8778</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,85%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1706</t>
+          <t>1902</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10819</t>
+          <t>10876</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>23023</t>
+          <t>22329</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35529</t>
+          <t>35662</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>54,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10335</t>
+          <t>10461</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20591</t>
+          <t>20546</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>76,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>37182</t>
+          <t>35427</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53711</t>
+          <t>53218</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>54,62%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>78,18%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3669</t>
+          <t>3630</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15419</t>
+          <t>16312</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>39,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4010</t>
+          <t>4038</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13557</t>
+          <t>13354</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9798</t>
+          <t>9933</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>24668</t>
+          <t>25226</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>37,06%</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8377</t>
+          <t>8867</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>874</t>
+          <t>875</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8376</t>
+          <t>7822</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>31,16%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>2107</t>
+          <t>1973</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12797</t>
+          <t>12981</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,07%</t>
         </is>
       </c>
     </row>
@@ -2436,97 +2436,97 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
+      <c r="R19" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1829</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>2068</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2549,97 +2549,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2184</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>5,3%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>1829</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>2068</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>350705</t>
+          <t>349507</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>387769</t>
+          <t>387323</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>419435</t>
+          <t>416568</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>468948</t>
+          <t>466891</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>784114</t>
+          <t>783585</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>848876</t>
+          <t>846564</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>71,78%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>54696</t>
+          <t>54191</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>85743</t>
+          <t>84918</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>89343</t>
+          <t>89243</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>127370</t>
+          <t>127226</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,8%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>152566</t>
+          <t>149667</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>200229</t>
+          <t>198546</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,98%</t>
+          <t>16,84%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18763</t>
+          <t>18223</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>37949</t>
+          <t>39547</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>49479</t>
+          <t>49585</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>80589</t>
+          <t>79493</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>71607</t>
+          <t>73686</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>110888</t>
+          <t>110932</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>13779</t>
+          <t>12850</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>30022</t>
+          <t>29573</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>16379</t>
+          <t>17548</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>36832</t>
+          <t>39582</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>34821</t>
+          <t>34279</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>60266</t>
+          <t>60627</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10802</t>
+          <t>11014</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>26520</t>
+          <t>27032</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>25095</t>
+          <t>25012</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>50026</t>
+          <t>49328</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>41749</t>
+          <t>40948</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>68780</t>
+          <t>69230</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,87%</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el nivel de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2012</t>
+          <t>Población según el grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>265941</t>
+          <t>262776</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>304972</t>
+          <t>304961</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,7 +3707,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>350946</t>
+          <t>349132</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>400441</t>
+          <t>400817</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,31%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>63,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>630045</t>
+          <t>629379</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>698040</t>
+          <t>694239</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>60,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,55%</t>
+          <t>66,18%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20728</t>
+          <t>20705</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42833</t>
+          <t>42346</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>63271</t>
+          <t>63778</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>95984</t>
+          <t>97255</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>90568</t>
+          <t>91199</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>129898</t>
+          <t>131570</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,63%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>12,54%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22998</t>
+          <t>23340</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>45868</t>
+          <t>47366</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>40431</t>
+          <t>40528</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>68861</t>
+          <t>67734</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>69625</t>
+          <t>71034</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>104941</t>
+          <t>106673</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,17%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21788</t>
+          <t>21980</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>46749</t>
+          <t>47075</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46929</t>
+          <t>47808</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78398</t>
+          <t>78986</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,47 +4081,47 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
+          <t>7,53%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>12,45%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>95284</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>77622</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>114714</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>9,08%</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
           <t>7,4%</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>12,35%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>95284</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>77261</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>116736</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>9,08%</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>7,37%</t>
-        </is>
-      </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,94%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20416</t>
+          <t>20502</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>44311</t>
+          <t>44743</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>49192</t>
+          <t>49116</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>80018</t>
+          <t>80386</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,67%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>74067</t>
+          <t>76419</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>115117</t>
+          <t>114761</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,94%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>88366</t>
+          <t>87575</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>105976</t>
+          <t>106177</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,47%</t>
+          <t>73,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,31%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>53579</t>
+          <t>52526</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69820</t>
+          <t>70187</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,05%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>147748</t>
+          <t>147171</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>172777</t>
+          <t>171303</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>84,91%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>991</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8301</t>
+          <t>8884</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5505</t>
+          <t>5326</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19267</t>
+          <t>20315</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>24,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7842</t>
+          <t>8189</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>24704</t>
+          <t>25718</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,75%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3078</t>
+          <t>3097</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14954</t>
+          <t>14857</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1006</t>
+          <t>988</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9101</t>
+          <t>9954</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6004</t>
+          <t>6017</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19386</t>
+          <t>19177</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,51%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2949</t>
+          <t>2071</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>15737</t>
+          <t>16024</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6461</t>
+          <t>6640</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4005</t>
+          <t>4071</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18444</t>
+          <t>18286</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>991</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8239</t>
+          <t>9067</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1091</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10290</t>
+          <t>10213</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>12,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>2246</t>
+          <t>3013</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13366</t>
+          <t>15267</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19744</t>
+          <t>19534</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>74,3%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12774</t>
+          <t>12663</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21159</t>
+          <t>21101</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>56,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35622</t>
+          <t>36091</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46549</t>
+          <t>46520</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>72,96%</t>
+          <t>73,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,29%</t>
         </is>
       </c>
     </row>
@@ -5169,97 +5169,97 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1109</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>2296</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>4852</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>4,98%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>21,81%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="R17" s="2" t="inlineStr">
         <is>
           <t>1109</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="S17" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>6026</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>4,98%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>5637</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>27,09%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>1109</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>5805</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>2,27%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,55%</t>
         </is>
       </c>
     </row>
@@ -5287,7 +5287,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5362</t>
+          <t>5089</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,62 +5317,62 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>1043</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>2222</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>4511</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>9,99%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>1043</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>6047</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>2,14%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,39%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6223</t>
+          <t>4692</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6585</t>
+          <t>7114</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,6%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>940</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8521</t>
+          <t>8757</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,94%</t>
         </is>
       </c>
     </row>
@@ -5508,97 +5508,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1100</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>2296</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5753</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>4,94%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>8,64%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>25,86%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>1100</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>5031</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>4,94%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>5529</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>2,25%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>22,61%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>1100</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>4900</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>11,32%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>386166</t>
+          <t>387230</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>430498</t>
+          <t>431970</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>426639</t>
+          <t>426276</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>481433</t>
+          <t>482405</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>57,66%</t>
+          <t>57,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>65,2%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>831654</t>
+          <t>829448</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>900768</t>
+          <t>899441</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>63,83%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>69,21%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>23130</t>
+          <t>22901</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>45766</t>
+          <t>46736</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>73865</t>
+          <t>75117</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>111021</t>
+          <t>112126</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>104604</t>
+          <t>106031</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>148147</t>
+          <t>149077</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>30542</t>
+          <t>31323</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>56894</t>
+          <t>56317</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>42672</t>
+          <t>43995</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>72222</t>
+          <t>76245</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>81308</t>
+          <t>81119</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>118606</t>
+          <t>122341</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,41%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>28011</t>
+          <t>29401</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>55415</t>
+          <t>55607</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>52164</t>
+          <t>53111</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>83786</t>
+          <t>85077</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>86439</t>
+          <t>86608</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>130159</t>
+          <t>129240</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,95%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>23222</t>
+          <t>22985</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>48479</t>
+          <t>47887</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>53876</t>
+          <t>51556</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>87560</t>
+          <t>84959</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>81930</t>
+          <t>81616</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>120648</t>
+          <t>122458</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,42%</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el nivel de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2016</t>
+          <t>Población según el grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>241212</t>
+          <t>240643</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>272139</t>
+          <t>272275</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,9%</t>
+          <t>76,94%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>315660</t>
+          <t>313817</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>363530</t>
+          <t>362927</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,9%</t>
+          <t>56,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,53%</t>
+          <t>65,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>568567</t>
+          <t>567301</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>626755</t>
+          <t>625080</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>62,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>68,79%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18006</t>
+          <t>17795</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>36497</t>
+          <t>35849</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>47956</t>
+          <t>48575</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>78553</t>
+          <t>80731</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>71757</t>
+          <t>71925</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>110235</t>
+          <t>109110</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,01%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21299</t>
+          <t>20291</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>41155</t>
+          <t>41099</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>49811</t>
+          <t>49834</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>85158</t>
+          <t>83249</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6932,7 +6932,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,35%</t>
+          <t>15,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>76759</t>
+          <t>77381</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>115556</t>
+          <t>117600</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,94%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17404</t>
+          <t>17019</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>35388</t>
+          <t>33718</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>37695</t>
+          <t>36378</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69251</t>
+          <t>67232</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58252</t>
+          <t>58886</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>93007</t>
+          <t>94797</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,43%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9849</t>
+          <t>9604</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24411</t>
+          <t>24935</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24291</t>
+          <t>24408</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51346</t>
+          <t>51198</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>39116</t>
+          <t>39066</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>69548</t>
+          <t>68599</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7193,7 +7193,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,55%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>160590</t>
+          <t>158968</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>177100</t>
+          <t>176986</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>82,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>117811</t>
+          <t>117469</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>145651</t>
+          <t>147072</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>62,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>77,44%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>284309</t>
+          <t>284517</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>318158</t>
+          <t>318031</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,56%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4428</t>
+          <t>4252</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15752</t>
+          <t>14849</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18312</t>
+          <t>16701</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38534</t>
+          <t>38236</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>25231</t>
+          <t>24516</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>51391</t>
+          <t>48781</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>12,82%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3718</t>
+          <t>3640</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14760</t>
+          <t>15135</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4845</t>
+          <t>4884</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21364</t>
+          <t>20062</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11154</t>
+          <t>11571</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>29301</t>
+          <t>30215</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1801</t>
+          <t>2340</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10168</t>
+          <t>11640</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7373</t>
+          <t>7660</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>24697</t>
+          <t>25189</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>12339</t>
+          <t>11506</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>31752</t>
+          <t>30226</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -7790,7 +7790,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4228</t>
+          <t>4232</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7825,7 +7825,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>11974</t>
+          <t>12641</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>840</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13165</t>
+          <t>13549</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30987</t>
+          <t>30762</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40134</t>
+          <t>40115</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>73,73%</t>
+          <t>73,19%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18281</t>
+          <t>18445</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30540</t>
+          <t>30204</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>52406</t>
+          <t>53499</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>68307</t>
+          <t>68889</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,23%</t>
+          <t>91,0%</t>
         </is>
       </c>
     </row>
@@ -8133,7 +8133,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4457</t>
+          <t>5610</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1056</t>
+          <t>1062</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11178</t>
+          <t>11595</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2046</t>
+          <t>1313</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>14264</t>
+          <t>13566</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>17,92%</t>
         </is>
       </c>
     </row>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8111</t>
+          <t>7333</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,3%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6921</t>
+          <t>7384</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>21,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1542</t>
+          <t>1213</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11093</t>
+          <t>12002</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>15,85%</t>
         </is>
       </c>
     </row>
@@ -8359,7 +8359,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5620</t>
+          <t>6225</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,62 +8389,62 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1760</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>2376</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>5822</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1760</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>6045</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>2,32%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -8467,97 +8467,97 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1376</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>1912</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>6446</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>4,09%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>4,55%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>19,14%</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K20" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>1376</t>
         </is>
       </c>
-      <c r="L20" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>6650</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>4,09%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
+        <is>
+          <t>6964</t>
+        </is>
+      </c>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>19,75%</t>
-        </is>
-      </c>
-      <c r="Q20" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R20" s="2" t="inlineStr">
-        <is>
-          <t>1376</t>
-        </is>
-      </c>
-      <c r="S20" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" s="2" t="inlineStr">
-        <is>
-          <t>6917</t>
-        </is>
-      </c>
-      <c r="U20" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,2%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>443786</t>
+          <t>446946</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>481156</t>
+          <t>483456</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>82,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>469235</t>
+          <t>470729</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>529870</t>
+          <t>525485</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>60,43%</t>
+          <t>60,62%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>67,67%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>925831</t>
+          <t>927459</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>998178</t>
+          <t>996911</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>73,13%</t>
+          <t>73,04%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>26027</t>
+          <t>25446</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>46677</t>
+          <t>46601</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>75366</t>
+          <t>75693</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>115371</t>
+          <t>116634</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>15,02%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>108863</t>
+          <t>107826</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>155538</t>
+          <t>152522</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,17%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>29207</t>
+          <t>28722</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>53254</t>
+          <t>54256</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>60884</t>
+          <t>62224</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>99152</t>
+          <t>99416</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,8%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>98245</t>
+          <t>99983</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>141973</t>
+          <t>141759</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,32%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22585</t>
+          <t>22631</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>43226</t>
+          <t>42911</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>47485</t>
+          <t>49188</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>83027</t>
+          <t>82815</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>77217</t>
+          <t>78785</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>118587</t>
+          <t>118070</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,65%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10268</t>
+          <t>10311</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>26027</t>
+          <t>25436</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>28853</t>
+          <t>29576</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>58296</t>
+          <t>58079</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>43087</t>
+          <t>42783</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>75596</t>
+          <t>73886</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el nivel de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2023</t>
+          <t>Población según el grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9610,12 +9610,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>150445</t>
+          <t>150164</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>177479</t>
+          <t>176066</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9625,12 +9625,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,59%</t>
+          <t>56,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9645,12 +9645,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>216871</t>
+          <t>218378</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>248877</t>
+          <t>249070</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9660,12 +9660,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,99%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9680,12 +9680,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>377830</t>
+          <t>375272</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>419178</t>
+          <t>417928</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9695,12 +9695,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>54,72%</t>
         </is>
       </c>
     </row>
@@ -9723,12 +9723,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23392</t>
+          <t>23069</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39778</t>
+          <t>39054</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9738,12 +9738,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>63577</t>
+          <t>62785</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>86089</t>
+          <t>85952</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9793,12 +9793,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>90638</t>
+          <t>89717</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>118344</t>
+          <t>118091</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9808,12 +9808,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,46%</t>
         </is>
       </c>
     </row>
@@ -9836,12 +9836,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>12859</t>
+          <t>13531</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26417</t>
+          <t>26665</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9851,12 +9851,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>55110</t>
+          <t>53766</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>75697</t>
+          <t>75603</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9886,12 +9886,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,2%</t>
+          <t>15,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9906,12 +9906,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>70939</t>
+          <t>72465</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>95691</t>
+          <t>95837</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -9921,12 +9921,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,55%</t>
         </is>
       </c>
     </row>
@@ -9949,12 +9949,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27858</t>
+          <t>28070</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45905</t>
+          <t>45500</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9964,12 +9964,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9984,12 +9984,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>57875</t>
+          <t>58707</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>79848</t>
+          <t>79557</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>90719</t>
+          <t>92661</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>119421</t>
+          <t>120199</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,88%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,74%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11129</t>
+          <t>11019</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23184</t>
+          <t>23270</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>46627</t>
+          <t>48109</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>68714</t>
+          <t>68704</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>63717</t>
+          <t>62481</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>86793</t>
+          <t>86718</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -10292,12 +10292,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>217046</t>
+          <t>218052</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>237160</t>
+          <t>236934</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10307,12 +10307,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>79,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10327,12 +10327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>341798</t>
+          <t>341489</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>435471</t>
+          <t>432832</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10342,12 +10342,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10362,12 +10362,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>576065</t>
+          <t>575794</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>681217</t>
+          <t>680133</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,6%</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10765</t>
+          <t>10689</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24509</t>
+          <t>23645</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7229</t>
+          <t>7993</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>47951</t>
+          <t>48499</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17651</t>
+          <t>17583</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>60766</t>
+          <t>61255</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,36%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6540</t>
+          <t>6291</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16403</t>
+          <t>15513</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3197</t>
+          <t>2993</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23863</t>
+          <t>23185</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8237</t>
+          <t>8896</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>34466</t>
+          <t>34178</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,7%</t>
         </is>
       </c>
     </row>
@@ -10631,12 +10631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6960</t>
+          <t>6743</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16749</t>
+          <t>16999</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3912</t>
+          <t>4087</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27169</t>
+          <t>27056</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>9746</t>
+          <t>10018</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>36775</t>
+          <t>37294</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3368</t>
+          <t>3474</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12119</t>
+          <t>12541</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2588</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20714</t>
+          <t>20822</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>7121</t>
+          <t>5918</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>27712</t>
+          <t>26906</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -10974,12 +10974,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>81187</t>
+          <t>81237</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>93030</t>
+          <t>93229</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10989,12 +10989,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11009,12 +11009,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>51431</t>
+          <t>51247</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>61369</t>
+          <t>60732</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11024,12 +11024,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11044,12 +11044,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>136075</t>
+          <t>136157</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>151225</t>
+          <t>150824</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11059,12 +11059,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>86,4%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5227</t>
+          <t>5098</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14263</t>
+          <t>14806</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4638</t>
+          <t>4791</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>12283</t>
+          <t>11826</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>16,58%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11400</t>
+          <t>12043</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23726</t>
+          <t>23851</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,66%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1134</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9191</t>
+          <t>8864</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1450</t>
+          <t>1362</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6177</t>
+          <t>6296</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3371</t>
+          <t>3723</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>11626</t>
+          <t>12194</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -11318,7 +11318,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4079</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11348,12 +11348,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>805</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6180</t>
+          <t>6727</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1539</t>
+          <t>1565</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8129</t>
+          <t>7767</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,45%</t>
         </is>
       </c>
     </row>
@@ -11426,12 +11426,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>161</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5386</t>
+          <t>5515</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11446,7 +11446,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11466,7 +11466,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3459</t>
+          <t>3401</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11481,7 +11481,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>944</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6859</t>
+          <t>6381</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>462010</t>
+          <t>461739</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>496486</t>
+          <t>498605</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>72,0%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>590272</t>
+          <t>593528</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>845352</t>
+          <t>839918</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>57,69%</t>
+          <t>58,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>82,62%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1083794</t>
+          <t>1085999</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1337528</t>
+          <t>1371312</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>65,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>80,33%</t>
+          <t>82,36%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>45384</t>
+          <t>44886</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>68111</t>
+          <t>69032</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,99%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>53152</t>
+          <t>57606</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>139466</t>
+          <t>138083</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>105152</t>
+          <t>93667</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>192677</t>
+          <t>190181</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,42%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>25114</t>
+          <t>24938</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>43390</t>
+          <t>42165</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>39835</t>
+          <t>37981</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>103387</t>
+          <t>103452</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>73435</t>
+          <t>71173</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>134270</t>
+          <t>132828</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>7,98%</t>
         </is>
       </c>
     </row>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>38772</t>
+          <t>39023</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>60225</t>
+          <t>60628</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>44285</t>
+          <t>43752</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>111408</t>
+          <t>110589</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>83242</t>
+          <t>80826</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>158420</t>
+          <t>158160</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,5%</t>
         </is>
       </c>
     </row>
@@ -12108,12 +12108,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>18383</t>
+          <t>18189</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>33640</t>
+          <t>33590</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12123,12 +12123,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>33186</t>
+          <t>34718</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>91733</t>
+          <t>90083</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12158,12 +12158,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>63639</t>
+          <t>61411</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>113792</t>
+          <t>112163</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12193,12 +12193,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,74%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/LAWTONB_2R-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/LAWTONB_2R-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>249841</t>
+          <t>248164</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>281807</t>
+          <t>282281</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>66,5%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>356315</t>
+          <t>355243</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>403045</t>
+          <t>401957</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>615602</t>
+          <t>617355</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>671519</t>
+          <t>674059</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>70,15%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>43236</t>
+          <t>43164</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>68151</t>
+          <t>68611</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,26%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>77014</t>
+          <t>74653</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>112218</t>
+          <t>111126</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>126734</t>
+          <t>126416</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>170352</t>
+          <t>171734</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,87%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>11801</t>
+          <t>11822</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>27693</t>
+          <t>27458</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>44689</t>
+          <t>44790</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>76120</t>
+          <t>74986</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>62452</t>
+          <t>59313</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>96329</t>
+          <t>94081</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>9,79%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>11521</t>
+          <t>11667</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26826</t>
+          <t>27973</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>15340</t>
+          <t>14855</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>34517</t>
+          <t>34259</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>30912</t>
+          <t>30075</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54142</t>
+          <t>56227</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,85%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9265</t>
+          <t>9082</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23624</t>
+          <t>24116</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>22554</t>
+          <t>22611</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>46882</t>
+          <t>47076</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>35848</t>
+          <t>36608</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>64179</t>
+          <t>63670</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>65275</t>
+          <t>66351</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>79439</t>
+          <t>79463</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>74,11%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>90,19%</t>
+          <t>90,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41077</t>
+          <t>40411</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>54639</t>
+          <t>54777</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>64,96%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,83%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>111905</t>
+          <t>112339</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>131473</t>
+          <t>131084</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>74,46%</t>
+          <t>74,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>87,48%</t>
+          <t>87,22%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1747</t>
+          <t>1691</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>9989</t>
+          <t>9381</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1933</t>
+          <t>1923</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12564</t>
+          <t>11922</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>5431</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18820</t>
+          <t>17767</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>11,82%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2523</t>
+          <t>2549</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13324</t>
+          <t>12443</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>8173</t>
+          <t>8220</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3599</t>
+          <t>3842</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16007</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>10,85%</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5893</t>
+          <t>6072</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,7 +1794,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6856</t>
+          <t>6646</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,7 +1809,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>1098</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10302</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>5577</t>
+          <t>6118</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>925</t>
+          <t>905</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8778</t>
+          <t>8469</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>13,61%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1902</t>
+          <t>1829</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>10876</t>
+          <t>11589</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,71%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22329</t>
+          <t>22622</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35662</t>
+          <t>35703</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10461</t>
+          <t>10191</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20546</t>
+          <t>20044</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,91%</t>
+          <t>37,91%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,43%</t>
+          <t>74,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35427</t>
+          <t>36722</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>53218</t>
+          <t>53930</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>53,94%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>79,22%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3630</t>
+          <t>3360</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16312</t>
+          <t>15272</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>39,6%</t>
+          <t>37,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4038</t>
+          <t>4060</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13354</t>
+          <t>13492</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>50,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>9933</t>
+          <t>9358</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>25226</t>
+          <t>25413</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,06%</t>
+          <t>37,33%</t>
         </is>
       </c>
     </row>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8867</t>
+          <t>8413</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2343,7 +2343,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>873</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7822</t>
+          <t>7911</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1973</t>
+          <t>2058</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12981</t>
+          <t>12959</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,04%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>349507</t>
+          <t>349048</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>387323</t>
+          <t>388210</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>416568</t>
+          <t>416872</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>466891</t>
+          <t>467565</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>783585</t>
+          <t>784663</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>846564</t>
+          <t>844615</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,62%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>54191</t>
+          <t>52962</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>84918</t>
+          <t>83890</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,12 +2907,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>16,9%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>89243</t>
+          <t>87911</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>127226</t>
+          <t>126236</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>149667</t>
+          <t>151409</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>198546</t>
+          <t>199983</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,96%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>18223</t>
+          <t>18647</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>39547</t>
+          <t>39285</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>49585</t>
+          <t>50584</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>79493</t>
+          <t>81615</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>73686</t>
+          <t>73074</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>110932</t>
+          <t>110447</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>12850</t>
+          <t>13329</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>29573</t>
+          <t>29482</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>17548</t>
+          <t>16925</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>39582</t>
+          <t>37917</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>34279</t>
+          <t>33358</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>60627</t>
+          <t>59021</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11014</t>
+          <t>11062</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>27032</t>
+          <t>27075</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>25012</t>
+          <t>25103</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>49328</t>
+          <t>50238</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>40948</t>
+          <t>40762</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>69230</t>
+          <t>68586</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>262776</t>
+          <t>266238</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>304961</t>
+          <t>304991</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,59%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>349132</t>
+          <t>353301</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>400817</t>
+          <t>403047</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>55,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>63,17%</t>
+          <t>63,52%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>629379</t>
+          <t>628836</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>694239</t>
+          <t>695414</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>59,95%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>66,3%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20705</t>
+          <t>20817</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>42346</t>
+          <t>42480</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3820,12 +3820,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>63778</t>
+          <t>63954</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>97255</t>
+          <t>99253</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3855,12 +3855,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>91199</t>
+          <t>91172</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>131570</t>
+          <t>130219</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,54%</t>
+          <t>12,41%</t>
         </is>
       </c>
     </row>
@@ -3918,12 +3918,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23340</t>
+          <t>23059</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47366</t>
+          <t>46540</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3933,12 +3933,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,23%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3953,12 +3953,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>40528</t>
+          <t>39857</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>67734</t>
+          <t>68096</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3968,12 +3968,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>71034</t>
+          <t>69858</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>106673</t>
+          <t>106118</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4003,12 +4003,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>21980</t>
+          <t>22911</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47075</t>
+          <t>48301</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>47808</t>
+          <t>48207</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>78986</t>
+          <t>77805</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,45%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>77622</t>
+          <t>77596</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>114714</t>
+          <t>115598</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20502</t>
+          <t>20834</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>44743</t>
+          <t>43415</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>49116</t>
+          <t>48641</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>80386</t>
+          <t>79360</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>12,51%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>76419</t>
+          <t>76364</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>114761</t>
+          <t>114303</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>10,9%</t>
         </is>
       </c>
     </row>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>87575</t>
+          <t>88341</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>106177</t>
+          <t>105899</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>74,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52526</t>
+          <t>52259</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>70187</t>
+          <t>69218</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>62,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>147171</t>
+          <t>148139</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>171303</t>
+          <t>172129</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>85,32%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>997</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8884</t>
+          <t>8670</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5326</t>
+          <t>6048</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20315</t>
+          <t>20489</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>24,45%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8189</t>
+          <t>9061</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>25718</t>
+          <t>25380</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>12,58%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3097</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14857</t>
+          <t>15138</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>988</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>9954</t>
+          <t>9928</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>6017</t>
+          <t>5927</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19177</t>
+          <t>20142</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2071</t>
+          <t>2105</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16024</t>
+          <t>15848</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>13,5%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4753,7 +4753,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6640</t>
+          <t>6481</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4071</t>
+          <t>3190</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>18286</t>
+          <t>18711</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,28%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>967</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9067</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1072</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10213</t>
+          <t>10046</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3013</t>
+          <t>3110</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15267</t>
+          <t>13879</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>6,88%</t>
         </is>
       </c>
     </row>
@@ -5056,7 +5056,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>19534</t>
+          <t>19941</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>73,51%</t>
+          <t>75,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>12663</t>
+          <t>12089</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>21101</t>
+          <t>21102</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>56,92%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36091</t>
+          <t>36043</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46520</t>
+          <t>45929</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>95,29%</t>
+          <t>94,08%</t>
         </is>
       </c>
     </row>
@@ -5209,7 +5209,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>4852</t>
+          <t>5884</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5224,7 +5224,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>26,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>5637</t>
+          <t>5626</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5259,7 +5259,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,52%</t>
         </is>
       </c>
     </row>
@@ -5287,7 +5287,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5089</t>
+          <t>5334</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5357,7 +5357,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>4511</t>
+          <t>5143</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4692</t>
+          <t>4456</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7114</t>
+          <t>6768</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>914</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8757</t>
+          <t>8409</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,23%</t>
         </is>
       </c>
     </row>
@@ -5548,7 +5548,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>5753</t>
+          <t>6829</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>5529</t>
+          <t>5786</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,32%</t>
+          <t>11,85%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>387230</t>
+          <t>387017</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>431970</t>
+          <t>431741</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>426276</t>
+          <t>428978</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>482405</t>
+          <t>483429</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>57,62%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,34%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>829448</t>
+          <t>831355</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>899441</t>
+          <t>901050</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,21%</t>
+          <t>69,34%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>22901</t>
+          <t>23281</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>46736</t>
+          <t>45741</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>75117</t>
+          <t>75669</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>112126</t>
+          <t>113071</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,28%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>106031</t>
+          <t>103968</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>149077</t>
+          <t>148295</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>31323</t>
+          <t>30542</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>56317</t>
+          <t>57445</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>43995</t>
+          <t>43523</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>76245</t>
+          <t>72535</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>81119</t>
+          <t>80942</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>122341</t>
+          <t>121234</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>29401</t>
+          <t>28027</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>55607</t>
+          <t>55453</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>53111</t>
+          <t>51572</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>85077</t>
+          <t>82364</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>86608</t>
+          <t>86450</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>129240</t>
+          <t>127388</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,8%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>22985</t>
+          <t>23339</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>47887</t>
+          <t>48620</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>51556</t>
+          <t>51919</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>84959</t>
+          <t>85845</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>6,97%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>81616</t>
+          <t>81270</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>122458</t>
+          <t>123145</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -6651,12 +6651,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>240643</t>
+          <t>241840</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>272275</t>
+          <t>272702</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6666,12 +6666,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6686,12 +6686,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>313817</t>
+          <t>314136</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>362927</t>
+          <t>364249</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6701,12 +6701,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>56,57%</t>
+          <t>56,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>65,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>567301</t>
+          <t>569459</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>625080</t>
+          <t>626801</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,43%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>68,98%</t>
         </is>
       </c>
     </row>
@@ -6764,12 +6764,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>17795</t>
+          <t>18064</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>35849</t>
+          <t>36989</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,13%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>48575</t>
+          <t>48346</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>80731</t>
+          <t>80172</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>71925</t>
+          <t>70843</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>109110</t>
+          <t>108460</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,94%</t>
         </is>
       </c>
     </row>
@@ -6877,12 +6877,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>20291</t>
+          <t>20954</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>41099</t>
+          <t>40608</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6892,12 +6892,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>49834</t>
+          <t>51678</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>83249</t>
+          <t>85707</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>77381</t>
+          <t>77984</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>117600</t>
+          <t>116153</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,78%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>17019</t>
+          <t>16504</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33718</t>
+          <t>35078</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>36378</t>
+          <t>36505</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>67232</t>
+          <t>66675</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>58886</t>
+          <t>58565</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>94797</t>
+          <t>92637</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,19%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>9604</t>
+          <t>10120</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>24935</t>
+          <t>24875</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>24408</t>
+          <t>26036</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>51198</t>
+          <t>52484</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,46%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>39066</t>
+          <t>39308</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>68599</t>
+          <t>69873</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,69%</t>
         </is>
       </c>
     </row>
@@ -7333,12 +7333,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>158968</t>
+          <t>159850</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>176986</t>
+          <t>177278</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7348,12 +7348,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>82,57%</t>
+          <t>83,02%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,12 +7368,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>117469</t>
+          <t>117731</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>147072</t>
+          <t>146676</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7383,12 +7383,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>77,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7403,12 +7403,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>284517</t>
+          <t>285277</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>318031</t>
+          <t>319017</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7418,12 +7418,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>83,56%</t>
+          <t>83,82%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4252</t>
+          <t>4229</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14849</t>
+          <t>14952</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>16701</t>
+          <t>17114</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>38236</t>
+          <t>38633</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>24516</t>
+          <t>24657</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>48781</t>
+          <t>48953</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>12,82%</t>
+          <t>12,86%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3640</t>
+          <t>4148</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15135</t>
+          <t>15677</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4884</t>
+          <t>5098</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20062</t>
+          <t>21347</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>11571</t>
+          <t>11331</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>30215</t>
+          <t>29208</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,04%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,67%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2340</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11640</t>
+          <t>11364</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7660</t>
+          <t>7412</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25189</t>
+          <t>24790</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11506</t>
+          <t>11761</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>30226</t>
+          <t>31454</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -7790,7 +7790,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4232</t>
+          <t>5087</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7825,7 +7825,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12641</t>
+          <t>12765</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>840</t>
+          <t>831</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13549</t>
+          <t>11808</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7875,7 +7875,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -8015,12 +8015,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30762</t>
+          <t>30349</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>40115</t>
+          <t>40280</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8030,12 +8030,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>73,19%</t>
+          <t>72,21%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8050,12 +8050,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18445</t>
+          <t>17504</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>30204</t>
+          <t>30368</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8065,12 +8065,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>51,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>90,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8085,12 +8085,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>53499</t>
+          <t>53963</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>68889</t>
+          <t>69184</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>71,28%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,39%</t>
         </is>
       </c>
     </row>
@@ -8133,7 +8133,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5610</t>
+          <t>6169</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,35%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1062</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11595</t>
+          <t>12357</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1313</t>
+          <t>1294</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13566</t>
+          <t>13747</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>18,16%</t>
         </is>
       </c>
     </row>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7333</t>
+          <t>8181</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8261,7 +8261,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>19,47%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8281,7 +8281,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7384</t>
+          <t>7579</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8296,7 +8296,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1213</t>
+          <t>1239</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12002</t>
+          <t>10914</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>14,42%</t>
         </is>
       </c>
     </row>
@@ -8359,7 +8359,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6225</t>
+          <t>5298</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8374,7 +8374,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8429,7 +8429,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>5822</t>
+          <t>5635</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8444,7 +8444,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,44%</t>
         </is>
       </c>
     </row>
@@ -8507,7 +8507,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>6446</t>
+          <t>6865</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8522,7 +8522,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8542,7 +8542,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6964</t>
+          <t>8506</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8557,7 +8557,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,2%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>446946</t>
+          <t>445083</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>483456</t>
+          <t>481774</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>81,87%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8732,12 +8732,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>470729</t>
+          <t>469716</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>525485</t>
+          <t>526920</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8747,12 +8747,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,49%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>927459</t>
+          <t>927750</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>996911</t>
+          <t>997078</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>73,05%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>25446</t>
+          <t>25959</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>46601</t>
+          <t>48203</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,82 +8825,82 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
+          <t>8,19%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>94158</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>73994</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>114756</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>12,13%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>9,53%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>14,78%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>129416</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>108101</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>154710</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>9,48%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
           <t>7,92%</t>
         </is>
       </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="K23" s="2" t="inlineStr">
-        <is>
-          <t>94158</t>
-        </is>
-      </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>75693</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>116634</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
-        <is>
-          <t>12,13%</t>
-        </is>
-      </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>9,75%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>15,02%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>129416</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>107826</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>152522</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>9,48%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>7,9%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,33%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>28722</t>
+          <t>29525</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>54256</t>
+          <t>53278</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>62224</t>
+          <t>59841</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>99416</t>
+          <t>99107</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>12,76%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>99983</t>
+          <t>98304</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>141759</t>
+          <t>141774</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,7 +9008,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22631</t>
+          <t>22906</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>42911</t>
+          <t>43434</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>49188</t>
+          <t>48064</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>82815</t>
+          <t>81984</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>78785</t>
+          <t>79074</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>118070</t>
+          <t>117330</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>10311</t>
+          <t>10072</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25436</t>
+          <t>26042</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>29576</t>
+          <t>29416</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>58079</t>
+          <t>58134</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>42783</t>
+          <t>43507</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>73886</t>
+          <t>75162</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,51%</t>
         </is>
       </c>
     </row>
@@ -9605,32 +9605,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>164296</t>
+          <t>178419</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>150164</t>
+          <t>163717</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>176066</t>
+          <t>191636</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>61,81%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>66,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9640,32 +9640,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>233218</t>
+          <t>251183</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>218378</t>
+          <t>234773</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>249070</t>
+          <t>270002</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>46,84%</t>
+          <t>46,9%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>43,86%</t>
+          <t>43,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9675,32 +9675,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>397514</t>
+          <t>429602</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>375272</t>
+          <t>408332</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>417928</t>
+          <t>452152</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>49,14%</t>
+          <t>49,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>55,01%</t>
         </is>
       </c>
     </row>
@@ -9718,32 +9718,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>30334</t>
+          <t>33448</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23069</t>
+          <t>25601</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>39054</t>
+          <t>43638</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9753,32 +9753,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>73560</t>
+          <t>78570</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>62785</t>
+          <t>67914</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>85952</t>
+          <t>92227</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9788,32 +9788,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>103894</t>
+          <t>112018</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>89717</t>
+          <t>97894</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>118091</t>
+          <t>128824</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,67%</t>
         </is>
       </c>
     </row>
@@ -9831,32 +9831,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>18981</t>
+          <t>19219</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>13531</t>
+          <t>13564</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>26665</t>
+          <t>25892</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9866,67 +9866,67 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>64877</t>
+          <t>69584</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>53766</t>
+          <t>58642</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>75603</t>
+          <t>81936</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
+          <t>10,95%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>15,3%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>88804</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>76280</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>103200</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
           <t>10,8%</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>15,18%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>83858</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>72465</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>95837</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>10,98%</t>
-        </is>
-      </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,56%</t>
         </is>
       </c>
     </row>
@@ -9944,32 +9944,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>36160</t>
+          <t>38776</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28070</t>
+          <t>29662</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>45500</t>
+          <t>48706</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,12%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9979,67 +9979,67 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>68687</t>
+          <t>74648</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>58707</t>
+          <t>62887</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>79557</t>
+          <t>87221</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
+          <t>13,94%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>11,74%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>16,28%</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>113424</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>98420</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>129917</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
           <t>13,8%</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>11,79%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>15,98%</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>205</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>104847</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>92661</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>120199</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>13,73%</t>
-        </is>
-      </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,74%</t>
+          <t>15,81%</t>
         </is>
       </c>
     </row>
@@ -10057,32 +10057,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>16058</t>
+          <t>16480</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11019</t>
+          <t>11197</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23270</t>
+          <t>23198</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10092,32 +10092,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>57547</t>
+          <t>61610</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>48109</t>
+          <t>51796</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>68704</t>
+          <t>72658</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10127,32 +10127,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>73605</t>
+          <t>78090</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>62481</t>
+          <t>65142</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>86718</t>
+          <t>91949</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>8,18%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -10170,17 +10170,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>265829</t>
+          <t>286342</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>265829</t>
+          <t>286342</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>265829</t>
+          <t>286342</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10205,17 +10205,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>497889</t>
+          <t>535596</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>497889</t>
+          <t>535596</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>497889</t>
+          <t>535596</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10240,17 +10240,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>763718</t>
+          <t>821938</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>763718</t>
+          <t>821938</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>763718</t>
+          <t>821938</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10287,32 +10287,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>227652</t>
+          <t>253650</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>218052</t>
+          <t>241954</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>236934</t>
+          <t>262892</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,67%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,98%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>86,72%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10322,32 +10322,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>394678</t>
+          <t>208173</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>341489</t>
+          <t>196703</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>432832</t>
+          <t>217791</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>71,35%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>78,99%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10357,32 +10357,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>622330</t>
+          <t>461824</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>575794</t>
+          <t>445786</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>680133</t>
+          <t>477020</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>79,78%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>82,41%</t>
         </is>
       </c>
     </row>
@@ -10400,32 +10400,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16292</t>
+          <t>18607</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10689</t>
+          <t>12082</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23645</t>
+          <t>26641</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10435,32 +10435,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24659</t>
+          <t>27434</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7993</t>
+          <t>20647</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>48499</t>
+          <t>35671</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>12,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10470,32 +10470,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>40951</t>
+          <t>46041</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>17583</t>
+          <t>36062</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>61255</t>
+          <t>57193</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -10513,32 +10513,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10495</t>
+          <t>11835</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6291</t>
+          <t>7786</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15513</t>
+          <t>17992</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10548,32 +10548,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11357</t>
+          <t>12680</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2993</t>
+          <t>8775</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23185</t>
+          <t>19099</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>4,6%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10583,32 +10583,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>21853</t>
+          <t>24516</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8896</t>
+          <t>18124</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>34178</t>
+          <t>32121</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,55%</t>
         </is>
       </c>
     </row>
@@ -10626,32 +10626,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11376</t>
+          <t>12166</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6743</t>
+          <t>7683</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>16999</t>
+          <t>18976</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10661,32 +10661,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13186</t>
+          <t>16592</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4087</t>
+          <t>11011</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27056</t>
+          <t>23032</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10696,32 +10696,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>24562</t>
+          <t>28758</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10018</t>
+          <t>21966</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37294</t>
+          <t>38132</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>6,59%</t>
         </is>
       </c>
     </row>
@@ -10739,32 +10739,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>6822</t>
+          <t>6898</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3474</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12541</t>
+          <t>11912</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10774,32 +10774,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>10137</t>
+          <t>10826</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2800</t>
+          <t>6819</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20822</t>
+          <t>16107</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10809,32 +10809,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>16959</t>
+          <t>17724</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5918</t>
+          <t>11716</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>26906</t>
+          <t>24437</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,22%</t>
         </is>
       </c>
     </row>
@@ -10852,17 +10852,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>272637</t>
+          <t>303157</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>272637</t>
+          <t>303157</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>272637</t>
+          <t>303157</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10887,17 +10887,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>454017</t>
+          <t>275705</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>454017</t>
+          <t>275705</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>454017</t>
+          <t>275705</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10922,17 +10922,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>726654</t>
+          <t>578863</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>726654</t>
+          <t>578863</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>726654</t>
+          <t>578863</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -10969,32 +10969,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>88040</t>
+          <t>100546</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>81237</t>
+          <t>92753</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>93229</t>
+          <t>106060</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>78,68%</t>
+          <t>79,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11004,32 +11004,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>56376</t>
+          <t>66068</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>51247</t>
+          <t>59538</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>60732</t>
+          <t>70674</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>79,04%</t>
+          <t>79,74%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>71,85%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11039,32 +11039,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>144415</t>
+          <t>166614</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>136157</t>
+          <t>156809</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>150824</t>
+          <t>174019</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>83,32%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>78,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>87,02%</t>
         </is>
       </c>
     </row>
@@ -11082,32 +11082,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9045</t>
+          <t>8995</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5098</t>
+          <t>5124</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14806</t>
+          <t>15490</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>13,23%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11117,32 +11117,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8006</t>
+          <t>8709</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>4791</t>
+          <t>5260</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>11826</t>
+          <t>13895</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11152,32 +11152,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>17052</t>
+          <t>17704</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12043</t>
+          <t>12224</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>23851</t>
+          <t>24961</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>12,48%</t>
         </is>
       </c>
     </row>
@@ -11195,32 +11195,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3383</t>
+          <t>4147</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8864</t>
+          <t>10202</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11230,32 +11230,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3166</t>
+          <t>3622</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1362</t>
+          <t>1467</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6296</t>
+          <t>6859</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11265,32 +11265,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>6549</t>
+          <t>7769</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3723</t>
+          <t>4331</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>12194</t>
+          <t>14672</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -11308,7 +11308,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1131</t>
+          <t>1244</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -11318,12 +11318,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3993</t>
+          <t>4442</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -11333,7 +11333,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11343,32 +11343,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>2795</t>
+          <t>3406</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1002</t>
+          <t>1309</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6727</t>
+          <t>7067</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,41%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11378,32 +11378,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>3926</t>
+          <t>4650</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1565</t>
+          <t>2037</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7767</t>
+          <t>8919</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -11421,32 +11421,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1648</t>
+          <t>2186</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>596</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>5515</t>
+          <t>5805</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11456,7 +11456,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>981</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
@@ -11466,12 +11466,12 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>3401</t>
+          <t>3399</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
@@ -11481,7 +11481,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11491,32 +11491,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>2629</t>
+          <t>3235</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>1054</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>6381</t>
+          <t>7874</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -11534,17 +11534,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>103247</t>
+          <t>117118</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>103247</t>
+          <t>117118</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>103247</t>
+          <t>117118</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11569,17 +11569,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>71325</t>
+          <t>82855</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11604,17 +11604,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>174571</t>
+          <t>199973</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>174571</t>
+          <t>199973</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>174571</t>
+          <t>199973</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11651,32 +11651,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>479986</t>
+          <t>532615</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>461739</t>
+          <t>512917</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>498605</t>
+          <t>551051</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>72,59%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>77,7%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11686,32 +11686,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>684272</t>
+          <t>525425</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>593528</t>
+          <t>502883</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>839918</t>
+          <t>547039</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>66,87%</t>
+          <t>58,76%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>58,01%</t>
+          <t>56,24%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>61,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11721,32 +11721,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1164258</t>
+          <t>1058040</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1085999</t>
+          <t>1024849</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1371312</t>
+          <t>1085784</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>65,23%</t>
+          <t>64,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>67,83%</t>
         </is>
       </c>
     </row>
@@ -11764,22 +11764,22 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>55671</t>
+          <t>61051</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>44886</t>
+          <t>49392</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>69032</t>
+          <t>76363</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -11789,7 +11789,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11799,32 +11799,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>106225</t>
+          <t>114713</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>57606</t>
+          <t>100545</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>138083</t>
+          <t>129514</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11834,32 +11834,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>161897</t>
+          <t>175764</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>93667</t>
+          <t>157509</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>190181</t>
+          <t>196267</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>9,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>12,26%</t>
         </is>
       </c>
     </row>
@@ -11877,32 +11877,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>32859</t>
+          <t>35202</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>24938</t>
+          <t>26707</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>42165</t>
+          <t>45013</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,98%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,78%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11912,32 +11912,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>79400</t>
+          <t>85886</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>37981</t>
+          <t>74262</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>103452</t>
+          <t>99151</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>8,31%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11947,32 +11947,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>112260</t>
+          <t>121088</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>71173</t>
+          <t>107319</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>132828</t>
+          <t>140763</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,79%</t>
         </is>
       </c>
     </row>
@@ -11990,32 +11990,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>48668</t>
+          <t>52186</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>39023</t>
+          <t>40287</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>60628</t>
+          <t>65008</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12025,32 +12025,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>84667</t>
+          <t>94646</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>43752</t>
+          <t>81279</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>110589</t>
+          <t>108648</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12060,32 +12060,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>133335</t>
+          <t>146832</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>80826</t>
+          <t>129882</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>158160</t>
+          <t>166391</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>10,39%</t>
         </is>
       </c>
     </row>
@@ -12103,32 +12103,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>24527</t>
+          <t>25564</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>18189</t>
+          <t>19056</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>33590</t>
+          <t>34751</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12138,32 +12138,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>68666</t>
+          <t>73486</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>34718</t>
+          <t>61483</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>90083</t>
+          <t>85949</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>8,22%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12173,32 +12173,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>93193</t>
+          <t>99050</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>61411</t>
+          <t>85833</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>112163</t>
+          <t>116594</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,28%</t>
         </is>
       </c>
     </row>
@@ -12216,17 +12216,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>641712</t>
+          <t>706617</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>641712</t>
+          <t>706617</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>641712</t>
+          <t>706617</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12251,17 +12251,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1023231</t>
+          <t>894156</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1023231</t>
+          <t>894156</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1023231</t>
+          <t>894156</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12286,17 +12286,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1664943</t>
+          <t>1600773</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1664943</t>
+          <t>1600773</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1664943</t>
+          <t>1600773</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
